--- a/DATA/analysis/体检点数据类型来源对应_2026-08-14.xlsx
+++ b/DATA/analysis/体检点数据类型来源对应_2026-08-14.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="类型来源对应明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总对照" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提取漏斗" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="类型来源对应明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总对照" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,12 +46,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,10 +86,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -459,7 +460,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>环节</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>原始数据库</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>总图斑（26 图层）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>3268</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>住房/小区/街区三维度全部要素</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>提取·安全韧性</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>928</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>结构42+围护454+楼道240+燃气6+管线186</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>提取·民生基础</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>757</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>养老2+婴幼儿34+幼儿园11+学位31+停车140+充电桩84+电动车50+步行道24+活动场地27+未物业273+运动场地6+乱停乱放5+非成套31+适老化39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>提取小计</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1685</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>928 + 757 = 负面图斑全提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>排除·附加</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>数字化25 + 智慧化31（绿色智能=附加发展类）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>排除·设施点</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>中学设施点21 + 菜市场设施点34（设施数量·非问题）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>排除·覆盖率</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1472</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>中学覆盖率535 + 公园覆盖率515 + 菜市场覆盖率422（面积指标·点数多=覆盖好）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>排除小计</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1583</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56 + 55 + 1472</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>校验</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>3268 = 提取 + 排除</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3268</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1685 + 1583 = 3268 ✓</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -467,9 +662,9 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,12 +690,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>性质</t>
+          <t>提取/排除</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>提取去向（最终8类）</t>
+          <t>提取去向（8类）</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -515,898 +710,1006 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>住房</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>安全耐久</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>结构隐患住宅</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>安全·住房</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>安全韧性</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>住房</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>安全耐久</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>燃气隐患住宅</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>安全·市政管网</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>安全韧性</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>燃气归管网</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>住房</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>安全耐久</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>楼道隐患住宅</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>安全·安全消防</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>安全韧性</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>住房</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>安全耐久</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>围护隐患住宅</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>454</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>安全·住房</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>安全韧性</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>住房</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>功能完备</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>非成套住宅</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>民生·住房</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>住房</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>功能完备</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>管线管道破损住宅</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>186</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>安全·市政管网</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>安全韧性</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>管线归管网</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>住房</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>功能完备</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>适老化改造住宅</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>民生·住房</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>住房</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>绿色智能</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>数字化改造住宅</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>附加·排除</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—（不参与）</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>排除·附加</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>绿色智能=附加发展类</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>设施完善</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>养老未达标小区</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>民生·公服设施</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>设施完善</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>婴幼儿照护未达标</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>民生·公服设施</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>设施完善</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>幼儿园未达标</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>民生·公服设施</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>设施完善</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>小学学位缺口</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>民生·公服设施</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>设施完善</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>停车泊位缺口</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>民生·停车设施</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>设施完善</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>充电桩缺口</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>民生·停车设施</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>设施完善</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>电动车充电未配建</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>民生·停车设施</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>环境宜居</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>步行道不达标</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>民生·交通设施</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>环境宜居</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>公共活动场地未达标</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>民生·公服设施</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>管理健全</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>未实施物业小区</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>民生·物业街面</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>小区</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>管理健全</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>智慧化改造小区</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>附加·排除</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>—（不参与）</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>排除·附加</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>智慧化=附加发展类</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>街区</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>功能完善</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>中学（设施点）</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>排除·设施点</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>设施数量·非问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>街区</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>功能完善</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>中学覆盖率</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>535</v>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>覆盖率·排除</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>—（不参与）</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>排除·覆盖率</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>覆盖率=面积指标</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>街区</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>功能完善</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>公园覆盖率</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>515</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>覆盖率·排除</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>—（不参与）</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>排除·覆盖率</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>覆盖率=面积指标</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>街区</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>功能完善</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>菜市场（设施点）</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>排除·设施点</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>设施数量·非问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>街区</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>功能完善</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>菜市场覆盖率</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>422</v>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>覆盖率·排除</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>—（不参与）</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>排除·覆盖率</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>覆盖率=面积指标</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>街区</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>功能完善</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>多功能运动场地未达标</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D26" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>民生·公服设施</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>街区</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>整洁有序</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>乱停乱放车辆道路</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D27" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>负面</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>提取</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>民生·物业街面</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>线转点</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>26 图层 / 26 类图斑</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>3268</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>提取 1685 / 排除 1583</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3268 = 提取1685 + 排除1583</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1477,340 +1780,340 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>安全·住房</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>安全韧性</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>结构隐患42 + 围护隐患454</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>496</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>496</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>496</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>零丢失</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>安全·安全消防</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>安全韧性</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>楼道隐患240</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>零丢失</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>安全·市政管网</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>安全韧性</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>管线破损186 + 燃气隐患6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>零丢失</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>安全小计</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="2" t="n">
         <v>928</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="2" t="n">
         <v>928</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="2" t="n">
         <v>928</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>零丢失</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>民生·公服设施</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>养老2+婴幼儿34+幼儿园11+学位31+活动场地27+运动场地6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>2点落缝范围外</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>民生·住房</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>非成套31 + 适老化39</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>零丢失</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>民生·停车设施</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>泊位140+充电桩84+电动车50</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>274</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>274</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>274</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>零丢失</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>民生·交通设施</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>不达标步行道24</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>零丢失</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>民生·物业街面</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>民生基础</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>未物业273 + 乱停乱放5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>零丢失</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>民生小计</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="2" t="n">
         <v>757</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>757</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="2" t="n">
         <v>755</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2点落缝范围外</t>
         </is>

--- a/DATA/analysis/体检点数据类型来源对应_2026-08-14.xlsx
+++ b/DATA/analysis/体检点数据类型来源对应_2026-08-14.xlsx
@@ -1938,14 +1938,14 @@
         <v>111</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>2点落缝范围外</t>
+          <t>2点范围外忽略</t>
         </is>
       </c>
     </row>
@@ -2108,14 +2108,14 @@
         <v>757</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2点落缝范围外</t>
+          <t>2点范围外忽略</t>
         </is>
       </c>
     </row>
